--- a/Codelist Excel Files and Conversion Templates to XML/grp-astmD2488Brdr.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/grp-astmD2488Brdr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81E3609-979C-A946-957A-ABF65E359A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF648B87-81A5-CC4C-88EC-5ABF46189D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20020" yWindow="3440" windowWidth="35840" windowHeight="20900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15360" yWindow="3440" windowWidth="35840" windowHeight="20900" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DictionaryName" sheetId="3" r:id="rId1"/>
@@ -1076,10 +1076,10 @@
     <t>Well to poorly graded sand</t>
   </si>
   <si>
-    <t>//diggs:Lithology/diggs:classificationSymbol</t>
-  </si>
-  <si>
     <t>grp-astmD2488Brdr</t>
+  </si>
+  <si>
+    <t>//diggs:LithologyObservation//diggs:classificationSymbol</t>
   </si>
 </sst>
 </file>
@@ -1885,7 +1885,7 @@
         <v>233</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>234</v>
@@ -2866,7 +2866,7 @@
         <v>236</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2878,7 +2878,7 @@
         <v>241</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2890,7 +2890,7 @@
         <v>244</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2902,7 +2902,7 @@
         <v>247</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2914,7 +2914,7 @@
         <v>250</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2926,7 +2926,7 @@
         <v>253</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2938,7 +2938,7 @@
         <v>256</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2950,7 +2950,7 @@
         <v>259</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2962,7 +2962,7 @@
         <v>262</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2974,7 +2974,7 @@
         <v>265</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2986,7 +2986,7 @@
         <v>268</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2998,7 +2998,7 @@
         <v>271</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -3010,7 +3010,7 @@
         <v>274</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -3022,7 +3022,7 @@
         <v>277</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -3034,7 +3034,7 @@
         <v>280</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3046,7 +3046,7 @@
         <v>283</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3058,7 +3058,7 @@
         <v>286</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3070,7 +3070,7 @@
         <v>289</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3082,7 +3082,7 @@
         <v>292</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3094,7 +3094,7 @@
         <v>295</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3106,7 +3106,7 @@
         <v>298</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3118,7 +3118,7 @@
         <v>301</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3130,7 +3130,7 @@
         <v>304</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3142,7 +3142,7 @@
         <v>307</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3154,7 +3154,7 @@
         <v>310</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3166,7 +3166,7 @@
         <v>313</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3178,7 +3178,7 @@
         <v>316</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3190,7 +3190,7 @@
         <v>319</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3202,7 +3202,7 @@
         <v>322</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3214,7 +3214,7 @@
         <v>325</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3226,7 +3226,7 @@
         <v>328</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3238,7 +3238,7 @@
         <v>331</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3250,7 +3250,7 @@
         <v>334</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3262,7 +3262,7 @@
         <v>337</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3274,7 +3274,7 @@
         <v>340</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -3286,7 +3286,7 @@
         <v>343</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
